--- a/submission/COMAVI_v7.12_SI/S1_Table.xlsx
+++ b/submission/COMAVI_v7.12_SI/S1_Table.xlsx
@@ -55,8 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -423,26 +424,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Supporting information item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>sheet</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>source item in the reviewed manuscript</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>caption</t>
         </is>
@@ -451,102 +458,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>S1 Table</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>benchmark_variants</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>S1 Table</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>S1 Table. The 61 benchmark variants. Every variant scored in this paper, with the clinical annotation, the expected mechanism defined from primary literature before COMAVI results were considered, the structural-context tier, COMAVI's graded agreement at the 2.5 kcal/mol reference threshold, and the</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S1 Table, benchmark_variants sheet. The 61 benchmark variants. Every variant scored in this paper, with the clinical annotation, the expected mechanism defined from primary literature before COMAVI results were considered, the structural-context tier, COMAVI's graded agreement at the 2.5 kcal/mol reference threshold, and the (S1 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>S1 Table</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>evidence_composition</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>S2 Table</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S2 Table. Evidence composition by category.</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>S1 Table, evidence_composition sheet. Evidence composition by category. (S2 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>S1 Table</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>model_scope</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>S3 Table</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>S3 Table. Model-scope and mechanism-eligibility framework.</t>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>S1 Table, model_scope sheet. Model-scope and mechanism-eligibility framework. (S3 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>S1 Table</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>context_comparators</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>S4 Table</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>S4 Table. Structural-context comparator analyses on the same 47-variant population.</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S1 Table, context_comparators sheet. Structural-context comparator analyses on the same 47-variant population. (S4 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>S1 Table</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>denominator_sensitivity</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>S5 Table</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>S5 Table. Denominator and eligibility sensitivity analyses.</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>S1 Table, denominator_sensitivity sheet. Denominator and eligibility sensitivity analyses. (S5 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>S1 Table</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>fold_binding_disagreements</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>S6 Table</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>S6 Table. Directly measured or curated fold and binding disagreements at the 2.5 kcal/mol reference.</t>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>S1 Table, fold_binding_disagreements sheet. Directly measured or curated fold and binding disagreements at the 2.5 kcal/mol reference. (S6 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
@@ -561,286 +598,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="58" customWidth="1" min="11" max="11"/>
-    <col width="58" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="32" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Gene</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Variant</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Clinical annotation</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Expected mechanism</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Structural tier</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Agreement at 2.5</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Agreement 1.0/1.5/2.0/2.5/SAP</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Committed axes</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence class</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence basis</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Citation</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Pred ΔΔG subunit</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Pred ΔΔG in complex</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Pred ΔΔG binding</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Measured ΔΔG</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Structure</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BRCA1 BRCT tandem domain (fold only)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>brca1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A1843P</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fold destabilization</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>consistent</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>C/C/C/C/C</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>monomer</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +4.89 kcal/mol</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Rowling, Cook &amp; Itzhaki 2010 JBC 285:20080 (PMID 20452977; PMC2888420), Table S1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1JNX.pdb</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S1 Table, benchmark_variants sheet. The 61 benchmark variants. Every variant scored in this paper, with the clinical annotation, the expected mechanism defined from primary literature before COMAVI results were considered, the structural-context tier, COMAVI's graded agreement at the 2.5 kcal/mol reference threshold, and the (S1 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BRCA1 BRCT tandem domain (fold only)</t>
+          <t>System</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>brca1</t>
+          <t>Gene</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L1664P</t>
+          <t>Variant</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Clinical annotation</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fold destabilization</t>
+          <t>Expected mechanism</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Structural tier</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>Agreement at 2.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X/X/X/X/X</t>
+          <t>Agreement 1.0/1.5/2.0/2.5/SAP</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>monomer</t>
+          <t>Committed axes</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>Evidence class</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +1.18 kcal/mol</t>
+          <t>Evidence basis</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Rowling, Cook &amp; Itzhaki 2010 JBC 285:20080 (PMID 20452977; PMC2888420), Table S1</t>
+          <t>Citation</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>Pred ΔΔG subunit</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pred ΔΔG in complex</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Pred ΔΔG binding</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>Measured ΔΔG</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>1JNX.pdb</t>
+          <t>Structure</t>
         </is>
       </c>
     </row>
@@ -857,7 +724,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M1663K</t>
+          <t>A1843P</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -867,7 +734,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold destabilization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -897,7 +764,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = -0.03 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +4.89 kcal/mol</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -907,7 +774,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -922,7 +789,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -944,7 +811,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M1783T</t>
+          <t>L1664P</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -964,12 +831,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>C/C/C/C/X</t>
+          <t>X/X/X/X/X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -984,7 +851,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +3.73 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +1.18 kcal/mol</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -994,7 +861,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1009,7 +876,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1031,7 +898,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P1806A</t>
+          <t>M1663K</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1056,7 +923,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X/X/C/C/C</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1071,7 +938,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +0.06 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = -0.03 kcal/mol</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1081,7 +948,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1096,7 +963,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1118,7 +985,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>R1699L</t>
+          <t>M1783T</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1128,7 +995,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold destabilization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1138,12 +1005,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ungraded</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-/-/-/-/-</t>
+          <t>C/C/C/C/X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1158,7 +1025,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = -0.99 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +3.73 kcal/mol</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1168,7 +1035,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1183,7 +1050,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1205,7 +1072,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>R1699Q</t>
+          <t>P1806A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1225,12 +1092,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ungraded</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-/-/-/-/-</t>
+          <t>X/X/C/C/C</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1245,7 +1112,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = -1.83 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +0.06 kcal/mol</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1255,7 +1122,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1270,7 +1137,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1292,7 +1159,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>R1751Q</t>
+          <t>R1699L</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1302,7 +1169,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fold destabilization</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1312,12 +1179,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>ungraded</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X/X/X/X/X</t>
+          <t>-/-/-/-/-</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1332,7 +1199,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +1.57 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = -0.99 kcal/mol</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1342,7 +1209,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1357,7 +1224,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1379,7 +1246,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V1665M</t>
+          <t>R1699Q</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1389,7 +1256,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fold destabilization</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1399,12 +1266,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>ungraded</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>-/-/-/-/-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1419,7 +1286,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +2.22 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = -1.83 kcal/mol</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1429,7 +1296,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1444,7 +1311,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1466,7 +1333,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>V1736A</t>
+          <t>R1751Q</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1491,7 +1358,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C/X/X/X/X</t>
+          <t>X/X/X/X/X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1506,7 +1373,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +4.20 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +1.57 kcal/mol</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1516,7 +1383,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1531,7 +1398,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1553,7 +1420,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>V1808A</t>
+          <t>V1665M</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1593,7 +1460,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +2.40 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +2.22 kcal/mol</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1603,7 +1470,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1618,7 +1485,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1640,7 +1507,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Y1853C</t>
+          <t>V1736A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1660,12 +1527,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>C/X/X/X/X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1680,7 +1547,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +6.04 kcal/mol</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +4.20 kcal/mol</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1690,7 +1557,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1705,7 +1572,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1717,7 +1584,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BRCA1-BARD1 RING heterodimer</t>
+          <t>BRCA1 BRCT tandem domain (fold only)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1727,12 +1594,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C61G</t>
+          <t>V1808A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1742,69 +1609,69 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>C/C/C/P/P</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>BARD1 binding preserved despite fold loss; RING heterodimer fold disrupted by Zn-coordination loss; C61 is a Zn-coordinating ligand; RING fold lost on Zn release</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +2.40 kcal/mol</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Brzovic 1998 JBC 273:7795 (PMID 9520298); Roehm &amp; Berg 1997 Biochemistry 36:10240</t>
+          <t>Rowling, Cook &amp; Itzhaki 2010 JBC 285:20080 (PMID 20452977; PMC2888420), Table S1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>1JM7.pdb</t>
+          <t>1JNX.pdb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BRCA1-BARD1 RING heterodimer</t>
+          <t>BRCA1 BRCT tandem domain (fold only)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1814,22 +1681,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>E100Q</t>
+          <t>Y1853C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold destabilization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tier 4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1844,47 +1711,47 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>monomer</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>E3/E5</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>WT-like BARD1 interaction by Y2H; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred from WT-like two-hybrid function</t>
+          <t>GdmCl equilibrium unfolding: measured ddG_U-F = +6.04 kcal/mol</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Starita 2015 (Y2H interaction panel)</t>
+          <t>Rowling, Cook &amp; Itzhaki 2010 JBC 285:20080 (PMID 20452977; PMC2888420), Table S1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1JM7.pdb</t>
+          <t>1JNX.pdb</t>
         </is>
       </c>
     </row>
@@ -1901,32 +1768,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>K45R</t>
+          <t>C61G</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold destabilization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>C/C/C/P/P</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1936,27 +1803,27 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>E3/E5</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>WT-like BARD1 interaction by Y2H; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred from WT-like two-hybrid function</t>
+          <t>BARD1 binding preserved despite fold loss; RING heterodimer fold disrupted by Zn-coordination loss; C61 is a Zn-coordinating ligand; RING fold lost on Zn release</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Starita 2015 (Y2H interaction panel)</t>
+          <t>Brzovic 1998 JBC 273:7795 (PMID 9520298); Roehm &amp; Berg 1997 Biochemistry 36:10240</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1988,67 +1855,67 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>V11G</t>
+          <t>E100Q</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C/C/C/P/P</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3/E5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Moderate BARD1 binding loss by two-hybrid</t>
+          <t>WT-like BARD1 interaction by Y2H; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred from WT-like two-hybrid function</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Clark 2022 (mammalian two-hybrid)</t>
+          <t>Starita 2015 (Y2H interaction panel)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2065,22 +1932,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Calmodulin-Ca(v)1.2 IQ domain</t>
+          <t>BRCA1-BARD1 RING heterodimer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>calm1</t>
+          <t>brca1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>D96V</t>
+          <t>K45R</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2090,7 +1957,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2100,42 +1967,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X/X/C/C/C</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>none committed</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E3/E5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Whole-variant expectation (no axis committed): CPVT/LQTS. EF-hand III Ca2+ site. Allosteric mechanism: Ca2+ binding disrupted but target engagement may persist. pLDDT=69.5.</t>
+          <t>WT-like BARD1 interaction by Y2H; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred from WT-like two-hybrid function</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>see curation note</t>
+          <t>Starita 2015 (Y2H interaction panel)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2145,24 +2012,24 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>fold_calm1_cacna1c_model_0.pdb</t>
+          <t>1JM7.pdb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Calmodulin-Ca(v)1.2 IQ domain</t>
+          <t>BRCA1-BARD1 RING heterodimer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>calm1</t>
+          <t>brca1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>F142L</t>
+          <t>V11G</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2172,7 +2039,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2182,47 +2049,47 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>C/C/C/P/P</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>none committed</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Whole-variant expectation (no axis committed): C-terminal lobe LQTS. Near IQ motif contact. Crotti 2013.</t>
+          <t>Moderate BARD1 binding loss by two-hybrid</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>see curation note</t>
+          <t>Clark 2022 (mammalian two-hybrid)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2232,7 +2099,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>fold_calm1_cacna1c_model_0.pdb</t>
+          <t>1JM7.pdb</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2116,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N98S</t>
+          <t>D96V</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2264,7 +2131,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tier 4</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2274,7 +2141,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>X/X/C/C/C</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2289,7 +2156,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Whole-variant expectation (no axis committed): Same EF-hand III site as D96V. Crotti 2013.</t>
+          <t>Whole-variant expectation (no axis committed): CPVT/LQTS. EF-hand III Ca2+ site. Allosteric mechanism: Ca2+ binding disrupted but target engagement may persist. pLDDT=69.5.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2299,17 +2166,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2326,22 +2193,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Complement factor H-C3b</t>
+          <t>Calmodulin-Ca(v)1.2 IQ domain</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cfh</t>
+          <t>calm1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>I62V</t>
+          <t>F142L</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2351,7 +2218,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2366,22 +2233,22 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>none committed</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>E1/E3/E5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>SPR K_D 10-14 uM, WT-like; No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded by CD / thermal denaturation</t>
+          <t>Whole-variant expectation (no axis committed): C-terminal lobe LQTS. Near IQ motif contact. Crotti 2013.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Pechtl 2011 JBC 286:11082 (PMID 21270465), SPR</t>
+          <t>see curation note</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2391,12 +2258,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2406,24 +2273,24 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2WII_trim.pdb</t>
+          <t>fold_calm1_cacna1c_model_0.pdb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Complement factor H-C3b</t>
+          <t>Calmodulin-Ca(v)1.2 IQ domain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cfh</t>
+          <t>calm1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>R53H</t>
+          <t>N98S</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2448,42 +2315,42 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X/C/C/C/C</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>none committed</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>E1/E3/E5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>SPR K_D ~12 uM, comparable to WT; No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded by CD / thermal denaturation</t>
+          <t>Whole-variant expectation (no axis committed): Same EF-hand III site as D96V. Crotti 2013.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Pechtl 2011 JBC 286:11082 (PMID 21270465), SPR</t>
+          <t>see curation note</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2493,7 +2360,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2WII_trim.pdb</t>
+          <t>fold_calm1_cacna1c_model_0.pdb</t>
         </is>
       </c>
     </row>
@@ -2510,32 +2377,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>R78G</t>
+          <t>I62V</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P/P/P/P/P</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2550,7 +2417,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SPR K_D &gt; 35 uM (binding effectively abolished); No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded by CD / thermal denaturation</t>
+          <t>SPR K_D 10-14 uM, WT-like; No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded by CD / thermal denaturation</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2560,17 +2427,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2587,17 +2454,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hemoglobin alpha-beta dimer</t>
+          <t>Complement factor H-C3b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hbb</t>
+          <t>cfh</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E6V</t>
+          <t>R53H</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2612,7 +2479,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2622,7 +2489,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>X/C/C/C/C</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2632,32 +2499,32 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E1/E3/E5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>HbS assembles normally -- pathogenicity arises from deoxy-state polymerization at a surface patch, not from alpha1-beta1 interface disruption; Native tetramer; assembly unaffected; Native beta-subunit fold; the lesion is intermolecular</t>
+          <t>SPR K_D ~12 uM, comparable to WT; No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded by CD / thermal denaturation</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Eaton &amp; Hofrichter 1990 (HbS polymerization)</t>
+          <t>Pechtl 2011 JBC 286:11082 (PMID 21270465), SPR</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2667,24 +2534,24 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2HHB.pdb</t>
+          <t>2WII_trim.pdb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hemoglobin tetramer</t>
+          <t>Complement factor H-C3b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hbb</t>
+          <t>cfh</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>N102T</t>
+          <t>R78G</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2694,7 +2561,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fold and interface</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2714,54 +2581,54 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>binding, fold_complex</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E1/E3/E5</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Hb Kansas: alpha1-beta2 H-bond loss, reduced tetramer assembly energy (~1.5 kcal/mol); Coupled reading of the same assembly measurement</t>
+          <t>SPR K_D &gt; 35 uM (binding effectively abolished); No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded by CD / thermal denaturation</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Bonaventura &amp; Riggs 1968 JBC (Hb Kansas)</t>
+          <t>Pechtl 2011 JBC 286:11082 (PMID 21270465), SPR</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2HHB.pdb</t>
+          <t>2WII_trim.pdb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hemoglobin tetramer</t>
+          <t>Hemoglobin alpha-beta dimer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2771,7 +2638,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>W37A</t>
+          <t>E6V</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2781,12 +2648,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fold and interface</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2801,42 +2668,42 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>binding, fold_complex</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +5.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
+          <t>HbS assembles normally -- pathogenicity arises from deoxy-state polymerization at a surface patch, not from alpha1-beta1 interface disruption; Native tetramer; assembly unaffected; Native beta-subunit fold; the lesion is intermolecular</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Kiger / Kwiatkowski Biochemistry 1998 (PMID 9521754 equilibrium assembly dG; PMID 9521753 kinetics)</t>
+          <t>Eaton &amp; Hofrichter 1990 (HbS polymerization)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2858,7 +2725,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>W37E</t>
+          <t>N102T</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2878,12 +2745,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>P/P/P/P/P</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2898,32 +2765,32 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +9.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
+          <t>Hb Kansas: alpha1-beta2 H-bond loss, reduced tetramer assembly energy (~1.5 kcal/mol); Coupled reading of the same assembly measurement</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Kiger / Kwiatkowski Biochemistry 1998 (PMID 9521754 equilibrium assembly dG; PMID 9521753 kinetics)</t>
+          <t>Bonaventura &amp; Riggs 1968 JBC (Hb Kansas)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2945,7 +2812,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>W37G</t>
+          <t>W37A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2985,7 +2852,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +7.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
+          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +5.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2995,22 +2862,22 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3032,7 +2899,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>W37Y</t>
+          <t>W37E</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3047,17 +2914,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C/C/P/P/P</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3072,7 +2939,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +2.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
+          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +9.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3082,22 +2949,22 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>5.88</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3109,32 +2976,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KRAS-CRAF RBD</t>
+          <t>Hemoglobin tetramer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kras</t>
+          <t>hbb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>G12D</t>
+          <t>W37G</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pathogenic (gain of function)</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold and interface</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3144,139 +3011,139 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X/X/X/C/C</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>WT-like RAF1 binding; impaired GTP hydrolysis. G12 is 13.6 A from RAF1</t>
+          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +7.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Hunter 2015</t>
+          <t>Kiger / Kwiatkowski Biochemistry 1998 (PMID 9521754 equilibrium assembly dG; PMID 9521753 kinetics)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6XI7.pdb</t>
+          <t>2HHB.pdb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KRAS-CRAF RBD</t>
+          <t>Hemoglobin tetramer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>kras</t>
+          <t>hbb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>G12V</t>
+          <t>W37Y</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pathogenic (gain of function)</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold and interface</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>C/C/P/P/P</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>WT-like RAF1 binding; impaired GTP hydrolysis</t>
+          <t>Equilibrium dimer-&gt;tetramer assembly ddG = +2.0 kcal/mol; Same assembly-energy measurement; the fold-in-complex token is a coupled reading of the assembly ddG, not an independent subunit-stability measurement</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Hunter 2015</t>
+          <t>Kiger / Kwiatkowski Biochemistry 1998 (PMID 9521754 equilibrium assembly dG; PMID 9521753 kinetics)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6XI7.pdb</t>
+          <t>2HHB.pdb</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3160,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Q61H</t>
+          <t>G12D</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3308,7 +3175,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tier 4</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3318,7 +3185,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>X/X/X/C/C</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3333,7 +3200,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Preserved RAF binding; switch-II hydrolysis defect. Q61 is 11.1 A from RAF1</t>
+          <t>WT-like RAF1 binding; impaired GTP hydrolysis. G12 is 13.6 A from RAF1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3343,12 +3210,12 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3370,22 +3237,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MLH1-PMS2 C-terminal heterodimer</t>
+          <t>KRAS-CRAF RBD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>pms2</t>
+          <t>kras</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>G857A</t>
+          <t>G12V</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic (gain of function)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3395,7 +3262,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3410,37 +3277,37 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>gnomAD AF 28%; ClinVar BA1 stand-alone benign</t>
+          <t>WT-like RAF1 binding; impaired GTP hydrolysis</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>gnomAD; ClinVar BA1</t>
+          <t>Hunter 2015</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3450,29 +3317,29 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>fold_mlh1_pms2_model_0.pdb</t>
+          <t>6XI7.pdb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MLH1-PMS2 C-terminal heterodimer</t>
+          <t>KRAS-CRAF RBD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>mlh1</t>
+          <t>kras</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>H718Y</t>
+          <t>Q61H</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic (gain of function)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3482,7 +3349,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3492,37 +3359,37 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X/C/C/C/C</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>binding, fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>E2/E5</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Proficient MMR implies the MLH1-PMS2 interaction survived; No assembly-context stability measurement; token inferred from the intact monomer fold</t>
+          <t>Preserved RAF binding; switch-II hydrolysis defect. Q61 is 11.1 A from RAF1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Raevaara 2005 (MMR activity)</t>
+          <t>Hunter 2015</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3537,7 +3404,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>fold_mlh1_pms2_model_0.pdb</t>
+          <t>6XI7.pdb</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3416,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>mlh1</t>
+          <t>pms2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>K618E</t>
+          <t>G857A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3579,42 +3446,42 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X/C/C/C/C</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Non-damaging in functional assay</t>
+          <t>gnomAD AF 28%; ClinVar BA1 stand-alone benign</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Drost 2019 (functional assay)</t>
+          <t>gnomAD; ClinVar BA1</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3641,67 +3508,67 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L749P</t>
+          <t>H718Y</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C/C/P/P/P</t>
+          <t>X/C/C/C/C</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E2/E5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>PMS2 co-IP 30% of WT</t>
+          <t>Proficient MMR implies the MLH1-PMS2 interaction survived; No assembly-context stability measurement; token inferred from the intact monomer fold</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Kosinski 2010 (PMS2 co-IP, MMR activity)</t>
+          <t>Raevaara 2005 (MMR activity)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3728,32 +3595,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Q542L</t>
+          <t>K618E</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P/P/P/P/P</t>
+          <t>X/C/C/C/C</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3763,32 +3630,32 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>PMS2 co-IP 54% of WT</t>
+          <t>Non-damaging in functional assay</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Kosinski 2010 (PMS2 co-IP, MMR activity)</t>
+          <t>Drost 2019 (functional assay)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3815,7 +3682,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R755W</t>
+          <t>L749P</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3825,7 +3692,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fold destabilization</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3835,17 +3702,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X/X/X/X/X</t>
+          <t>C/C/P/P/P</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3855,27 +3722,27 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>MAVE interaction score +0.617; PMS2 co-IP 82% -- binding preserved; MAVE abundance score -0.334: reduced cellular abundance</t>
+          <t>PMS2 co-IP 30% of WT</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MAVE abundance/interaction scores; Kosinski 2010 co-IP</t>
+          <t>Kosinski 2010 (PMS2 co-IP, MMR activity)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-9.66</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3902,67 +3769,67 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>V384D</t>
+          <t>Q542L</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>X/X/C/C/C</t>
+          <t>P/P/P/P/P</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>E3/E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Reclassified non-pathogenic; MMR-proficient; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred</t>
+          <t>PMS2 co-IP 54% of WT</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>InSiGHT expert-panel reclassification; rs63750447 AF ~8.9% EAS</t>
+          <t>Kosinski 2010 (PMS2 co-IP, MMR activity)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3979,17 +3846,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MSH2-MSH6 heterodimer</t>
+          <t>MLH1-PMS2 C-terminal heterodimer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>msh2</t>
+          <t>mlh1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A636P</t>
+          <t>R755W</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3999,12 +3866,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold destabilization</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4024,32 +3891,32 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>MSH2-MSH6 interaction intact; ATPase mismatch binding/release defect; MSH2 expression/stability preserved; ATPase mismatch binding/release defect</t>
+          <t>MAVE interaction score +0.617; PMS2 co-IP 82% -- binding preserved; MAVE abundance score -0.334: reduced cellular abundance</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ollila 2008 Hum Mutat 29:1355 (PMID 18951462); Ollila 2006 Gastroenterology (PMID 17101317)</t>
+          <t>MAVE abundance/interaction scores; Kosinski 2010 co-IP</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-9.66</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4059,29 +3926,29 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>fold_msh2_msh6_model_0.pdb</t>
+          <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MSH2-MSH6 heterodimer</t>
+          <t>MLH1-PMS2 C-terminal heterodimer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>msh2</t>
+          <t>mlh1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C697F</t>
+          <t>V384D</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4091,52 +3958,52 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X/X/X/X/X</t>
+          <t>X/X/C/C/C</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E3/E5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ATPase catalytic defect, protein stable, interaction intact</t>
+          <t>Reclassified non-pathogenic; MMR-proficient; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ollila 2008 Hum Mutat 29:1355 (PMID 18951462); Ollila 2006 Gastroenterology (PMID 17101317)</t>
+          <t>InSiGHT expert-panel reclassification; rs63750447 AF ~8.9% EAS</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>13.29</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4146,7 +4013,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>fold_msh2_msh6_model_0.pdb</t>
+          <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4030,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>G322D</t>
+          <t>A636P</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4178,22 +4045,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tier 4</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X/X/X/C/C</t>
+          <t>X/X/X/X/X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4203,7 +4070,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>MMR-proficient with interaction intact; gnomAD ~1.9%</t>
+          <t>MSH2-MSH6 interaction intact; ATPase mismatch binding/release defect; MSH2 expression/stability preserved; ATPase mismatch binding/release defect</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4213,12 +4080,12 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4250,7 +4117,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>G674R</t>
+          <t>C697F</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4265,7 +4132,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4290,22 +4157,22 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>MSH6 binding preserved by co-IP; MMR lost via Walker-A ATPase defect</t>
+          <t>ATPase catalytic defect, protein stable, interaction intact</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Jia 2021</t>
+          <t>Ollila 2008 Hum Mutat 29:1355 (PMID 18951462); Ollila 2006 Gastroenterology (PMID 17101317)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>13.29</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>15.26</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4337,7 +4204,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>N127S</t>
+          <t>G322D</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4352,7 +4219,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4362,7 +4229,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X/C/C/C/C</t>
+          <t>X/X/X/C/C</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4377,7 +4244,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>MSH6 IP, bandshift and MMR all WT-like</t>
+          <t>MMR-proficient with interaction intact; gnomAD ~1.9%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4387,12 +4254,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4414,27 +4281,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PI3K p110alpha-p85alpha</t>
+          <t>MSH2-MSH6 heterodimer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pik3ca</t>
+          <t>msh2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>E542K</t>
+          <t>G674R</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pathogenic (gain of function)</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4444,47 +4311,47 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P/P/P/P/P</t>
+          <t>X/X/X/X/X</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>binding, monomer</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>E3/E5</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Disrupts the nSH2 inhibitory contact, releasing autoinhibition; No subunit-stability assay; token inferred; helical-domain hotspot taken as fold-neutral</t>
+          <t>MSH6 binding preserved by co-IP; MMR lost via Walker-A ATPase defect</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Zhao &amp; Vogt 2008 PNAS</t>
+          <t>Jia 2021</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4494,34 +4361,34 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>fold_pik3ca_pik3r1_model_0.pdb</t>
+          <t>fold_msh2_msh6_model_0.pdb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PI3K p110alpha-p85alpha</t>
+          <t>MSH2-MSH6 heterodimer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pik3ca</t>
+          <t>msh2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>E545K</t>
+          <t>N127S</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pathogenic (gain of function)</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4531,47 +4398,47 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>C/C/X/X/X</t>
+          <t>X/C/C/C/C</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>binding, monomer</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>E3/E5</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Disrupts the nSH2 inhibitory contact, releasing autoinhibition; No subunit-stability assay; token inferred; helical-domain hotspot taken as fold-neutral</t>
+          <t>MSH6 IP, bandshift and MMR all WT-like</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Zhao &amp; Vogt 2008 PNAS</t>
+          <t>Ollila 2008 Hum Mutat 29:1355 (PMID 18951462); Ollila 2006 Gastroenterology (PMID 17101317)</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4581,7 +4448,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>fold_pik3ca_pik3r1_model_0.pdb</t>
+          <t>fold_msh2_msh6_model_0.pdb</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4465,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>H1047R</t>
+          <t>E542K</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4608,7 +4475,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4618,17 +4485,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X/X/X/C/C</t>
+          <t>P/P/P/P/P</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>binding, monomer</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4638,27 +4505,27 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Kinase C-lobe gain of function with p85 binding structurally unaffected; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred</t>
+          <t>Disrupts the nSH2 inhibitory contact, releasing autoinhibition; No subunit-stability assay; token inferred; helical-domain hotspot taken as fold-neutral</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Mandelker 2009</t>
+          <t>Zhao &amp; Vogt 2008 PNAS</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4680,72 +4547,72 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pik3r1</t>
+          <t>pik3ca</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M326I</t>
+          <t>E545K</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic (gain of function)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tier 4</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>C/C/X/X/X</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>binding, monomer</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E3/E5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>rs3730089, gnomAD MAF &gt; 10%: benign by frequency alone</t>
+          <t>Disrupts the nSH2 inhibitory contact, releasing autoinhibition; No subunit-stability assay; token inferred; helical-domain hotspot taken as fold-neutral</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>gnomAD (rs3730089)</t>
+          <t>Zhao &amp; Vogt 2008 PNAS</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4767,17 +4634,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pik3r1</t>
+          <t>pik3ca</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>N564D</t>
+          <t>H1047R</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Pathogenic (gain of function)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4792,12 +4659,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X/X/X/X/X</t>
+          <t>X/X/X/C/C</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4812,27 +4679,27 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Retains p110 binding, loses inhibition -- allosteric, not interface loss; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred</t>
+          <t>Kinase C-lobe gain of function with p85 binding structurally unaffected; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Wu / Jaiswal 2009</t>
+          <t>Mandelker 2009</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4849,72 +4716,72 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SMAD4-SMAD3 MH2 complex</t>
+          <t>PI3K p110alpha-p85alpha</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>smad4</t>
+          <t>pik3r1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>D351H</t>
+          <t>M326I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P/P/P/P/P</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Abolished phospho-Smad2/3 interaction by co-IP</t>
+          <t>rs3730089, gnomAD MAF &gt; 10%: benign by frequency alone</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>De Bosscher 2004 (co-IP)</t>
+          <t>gnomAD (rs3730089)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4929,29 +4796,29 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>fold_smad4_smad3_model_0.pdb</t>
+          <t>fold_pik3ca_pik3r1_model_0.pdb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SMAD4-SMAD3 MH2 complex</t>
+          <t>PI3K p110alpha-p85alpha</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>smad4</t>
+          <t>pik3r1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>I500T</t>
+          <t>N564D</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Pathogenic (gain of function)</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4966,47 +4833,47 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>X/X/C/C/C</t>
+          <t>X/X/X/X/X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>none committed</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E3/E5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Whole-variant expectation (no axis committed): LABEL CORRECTION. Myhre syndrome. Le Goff 2011: reduced ubiquitination → protein stabilization. Post-translational mechanism likely invisible to FoldX. Pipeline should call "no structural effect detected" — this is a correct structural call.</t>
+          <t>Retains p110 binding, loses inhibition -- allosteric, not interface loss; No assembly-context stability measurement; token inferred from the intact monomer fold; No subunit-stability assay; token inferred</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>see curation note</t>
+          <t>Wu / Jaiswal 2009</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5016,7 +4883,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>fold_smad4_smad3_model_0.pdb</t>
+          <t>fold_pik3ca_pik3r1_model_0.pdb</t>
         </is>
       </c>
     </row>
@@ -5033,62 +4900,62 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>I500V</t>
+          <t>D351H</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pathogenic (gain of function)</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>P/P/P/P/P</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>none committed</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Whole-variant expectation (no axis committed): Same mechanism as I500T. Le Goff 2011.</t>
+          <t>Abolished phospho-Smad2/3 interaction by co-IP</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>see curation note</t>
+          <t>De Bosscher 2004 (co-IP)</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5120,22 +4987,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>R361C</t>
+          <t>I500T</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Pathogenic (gain of function)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Interface disruption</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5145,42 +5012,42 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>X/X/C/C/C</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>none committed</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Completely abolished R-Smad interaction</t>
+          <t>Whole-variant expectation (no axis committed): LABEL CORRECTION. Myhre syndrome. Le Goff 2011: reduced ubiquitination → protein stabilization. Post-translational mechanism likely invisible to FoldX. Pipeline should call "no structural effect detected" — this is a correct structural call.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Lanauze 2021 (co-IP)</t>
+          <t>see curation note</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5197,22 +5064,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Troponin I-troponin C</t>
+          <t>SMAD4-SMAD3 MH2 complex</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>tnni3</t>
+          <t>smad4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>P82S</t>
+          <t>I500V</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic (gain of function)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5222,7 +5089,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tier 4</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5237,32 +5104,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>none committed</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>AF ~3% African-American: benign by frequency</t>
+          <t>Whole-variant expectation (no axis committed): Same mechanism as I500T. Le Goff 2011.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Frazier 2008; gnomAD</t>
+          <t>see curation note</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5277,24 +5144,24 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>fold_tnni3_tnnc1_model_0.pdb</t>
+          <t>fold_smad4_smad3_model_0.pdb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Troponin I-troponin C</t>
+          <t>SMAD4-SMAD3 MH2 complex</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>tnni3</t>
+          <t>smad4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>R145G</t>
+          <t>R361C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5304,22 +5171,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Interface disruption</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X/X/X/X/X</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5329,32 +5196,32 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>EC50 1.4 uM vs 0.8 uM WT: reduced inhibitory potency, actin affinity unchanged -- interface retained</t>
+          <t>Completely abolished R-Smad interaction</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Elliott 2000 JBC 275:22069; Takahashi / Kimura 2001 (PMID 11735257)</t>
+          <t>Lanauze 2021 (co-IP)</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5364,7 +5231,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>fold_tnni3_tnnc1_model_0.pdb</t>
+          <t>fold_smad4_smad3_model_0.pdb</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5248,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R145Q</t>
+          <t>P82S</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Pathogenic</t>
+          <t>Benign</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5396,52 +5263,52 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>inconsistent</t>
+          <t>consistent</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X/X/X/X/C</t>
+          <t>C/C/C/C/C</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>binding</t>
+          <t>binding, fold_complex, monomer</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Same class as R145G: reduced inhibition, actin affinity unchanged</t>
+          <t>AF ~3% African-American: benign by frequency</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Kimura 2001 (PMID 11735257)</t>
+          <t>Frazier 2008; gnomAD</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5468,7 +5335,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>R162W</t>
+          <t>R145G</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5478,57 +5345,57 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Interface, magnitude uncommitted</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ungraded</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-/-/-/-/-</t>
+          <t>X/X/X/X/X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>none committed</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Whole-variant expectation (no axis committed): LABEL CORRECTION. Elliott 2000: INCREASED TnC affinity, disrupted regulation. Interface stabilization, not disruption. Pipeline should call PPI stabilization.</t>
+          <t>EC50 1.4 uM vs 0.8 uM WT: reduced inhibitory potency, actin affinity unchanged -- interface retained</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>see curation note</t>
+          <t>Elliott 2000 JBC 275:22069; Takahashi / Kimura 2001 (PMID 11735257)</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5545,17 +5412,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VHL-elongin C</t>
+          <t>Troponin I-troponin C</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>vhl</t>
+          <t>tnni3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>L158Q</t>
+          <t>R145Q</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5565,57 +5432,57 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fold and interface</t>
+          <t>No modeled lesion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>inconsistent</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>C/C/C/C/P</t>
+          <t>X/X/X/X/C</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>binding, fold_complex</t>
+          <t>binding</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Disrupts VCB complex assembly</t>
+          <t>Same class as R145G: reduced inhibition, actin affinity unchanged</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Stebbins 1999 Science</t>
+          <t>Kimura 2001 (PMID 11735257)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5625,24 +5492,24 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>fold_vhl_tceb1_model_0.pdb</t>
+          <t>fold_tnni3_tnnc1_model_0.pdb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VHL-elongin C</t>
+          <t>Troponin I-troponin C</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>vhl</t>
+          <t>tnni3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>W117R</t>
+          <t>R162W</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5652,12 +5519,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Not committed</t>
+          <t>Interface, magnitude uncommitted</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5682,7 +5549,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Whole-variant expectation (no axis committed): RECLASSIFIED mechanism_control. W117 in β-domain HIF-binding pocket, not ElonginC face. Fold destab + preserved ElonginC binding.</t>
+          <t>Whole-variant expectation (no axis committed): LABEL CORRECTION. Elliott 2000: INCREASED TnC affinity, disrupted regulation. Interface stabilization, not disruption. Pipeline should call PPI stabilization.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5692,17 +5559,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5712,7 +5579,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>fold_vhl_tceb1_model_0.pdb</t>
+          <t>fold_tnni3_tnnc1_model_0.pdb</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5596,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Y98H</t>
+          <t>L158Q</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5739,7 +5606,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Fold and interface</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5754,7 +5621,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X/C/C/C/C</t>
+          <t>C/C/C/C/P</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5769,27 +5636,27 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>VCB assembly preserved while HIF binding is abolished (beta-domain HIF face, not the ElonginC face)</t>
+          <t>Disrupts VCB complex assembly</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Ohh 2000</t>
+          <t>Stebbins 1999 Science</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -5806,77 +5673,77 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VWF A1-GPIb alpha</t>
+          <t>VHL-elongin C</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>vwf</t>
+          <t>vhl</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A1381T</t>
+          <t>W117R</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Benign</t>
+          <t>Pathogenic</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>No modeled lesion</t>
+          <t>Not committed</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>consistent</t>
+          <t>ungraded</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C/C/C/C/C</t>
+          <t>-/-/-/-/-</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>binding, fold_complex, monomer</t>
+          <t>none committed</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>E1/E5</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Binding-competent by SPR; No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded, WT-like Tm</t>
+          <t>Whole-variant expectation (no axis committed): RECLASSIFIED mechanism_control. W117 in β-domain HIF-binding pocket, not ElonginC face. Fold destab + preserved ElonginC binding.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Tischer / Moon-Tasson / Auton 2025 J Thromb Haemost 23(4):1215-1228 (PMID 39756657); CD/DSC + SPR + shear-flow</t>
+          <t>see curation note</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5886,92 +5753,266 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>1SQ0.pdb</t>
+          <t>fold_vhl_tceb1_model_0.pdb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>VHL-elongin C</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>vhl</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Y98H</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pathogenic</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>No modeled lesion</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>consistent</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X/C/C/C/C</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>binding, fold_complex</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>VCB assembly preserved while HIF binding is abolished (beta-domain HIF face, not the ElonginC face)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Ohh 2000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>fold_vhl_tceb1_model_0.pdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>VWF A1-GPIb alpha</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>vwf</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>A1381T</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Benign</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>No modeled lesion</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tier 2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>consistent</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>C/C/C/C/C</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>binding, fold_complex, monomer</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>E1/E5</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Binding-competent by SPR; No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded, WT-like Tm</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Tischer / Moon-Tasson / Auton 2025 J Thromb Haemost 23(4):1215-1228 (PMID 39756657); CD/DSC + SPR + shear-flow</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>-0.00</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1SQ0.pdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VWF A1-GPIb alpha</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>vwf</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>R1334Q</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Pathogenic</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Interface disruption</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>P/P/P/P/P</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>binding, fold_complex, monomer</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>E1/E5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>GPIba binding lost by SPR and shear-flow adhesion; No assembly-context stability measurement; token inferred from the intact monomer fold; Natively folded with modestly reduced Tm -- below the destabilization threshold</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>Tischer / Moon-Tasson / Auton 2025 J Thromb Haemost 23(4):1215-1228 (PMID 39756657); CD/DSC + SPR + shear-flow</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>4.73</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>4.11</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>1SQ0.pdb</t>
         </is>
@@ -5988,128 +6029,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Axes</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Destabilizing</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>E1 quantitative energetic</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Direct or quantitative energetic evidence; includes one stabilizing expectation. One E1 monomer axis (BRCA1 R1699Q) carries a stabilizing rather than neutral or destabilizing expectation and is not shown in either column, so this row's Neutral and Destabilizing counts sum to 28 of 29.</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S1 Table, evidence_composition sheet. Evidence composition by category. (S2 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E2 quantitative functional</t>
+          <t>Evidence category</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Axes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Destabilizing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Quantitative functional readout coupled to the axis.</t>
+          <t>Interpretation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E3 qualitative experimental</t>
+          <t>E1 quantitative energetic</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qualitative experimental evidence; includes the two A636P neutral fold expectations.</t>
+          <t>Direct or quantitative energetic evidence; includes one stabilizing expectation. One E1 monomer axis (BRCA1 R1699Q) carries a stabilizing rather than neutral or destabilizing expectation and is not shown in either column, so this row's Neutral and Destabilizing counts sum to 28 of 29.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E4 population frequency</t>
+          <t>E2 quantitative functional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6119,42 +6113,96 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Population-supported neutral expectations.</t>
+          <t>Quantitative functional readout coupled to the axis.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>E3 qualitative experimental</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Qualitative experimental evidence; includes the two A636P neutral fold expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E4 population frequency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Population-supported neutral expectations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>E5 inferred</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Literature-supported axis state without an axis-specific assay; primarily neutral commitments.</t>
         </is>
@@ -6171,94 +6219,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Whole-variant treatment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Representable structural</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Known lesion maps to one or more supplied COMAVI energetic outputs.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Grade the complete applicable-axis pattern.</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S1 Table, model_scope sheet. Model-scope and mechanism-eligibility framework. (S3 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Structural context missing</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A required partner, ligand, modification, oligomer, or state is absent.</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Exclude whole-variant mechanism grading; retain independently gradeable axes.</t>
+          <t>Whole-variant treatment</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nonstructural or static-invisible</t>
+          <t>Representable structural</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Catalytic, regulatory, dynamic, aggregative, or post-translational mechanism outside static energetic outputs.</t>
+          <t>Known lesion maps to one or more supplied COMAVI energetic outputs.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>May be a committed benchmark negative only when literature supports the modeled axes.</t>
+          <t>Grade the complete applicable-axis pattern.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Structural context missing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A required partner, ligand, modification, oligomer, or state is absent.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Exclude whole-variant mechanism grading; retain independently gradeable axes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Nonstructural or static-invisible</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Catalytic, regulatory, dynamic, aggregative, or post-translational mechanism outside static energetic outputs.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>May be a committed benchmark negative only when literature supports the modeled axes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Mechanistically uncommitted</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Evidence does not establish a structural-versus-nonstructural pattern.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Exclude from whole-variant grading.</t>
         </is>
@@ -6275,10 +6330,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -6289,168 +6344,175 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Screen</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>TP/FN</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FP/TN</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sensitivity</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Specificity</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>PPV</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Balanced accuracy</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Within-system p</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Any pLDDT-passing interface</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>15/2</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7/23</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.882</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.767</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.682</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.824</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0018</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S1 Table, context_comparators sheet. Structural-context comparator analyses on the same 47-variant population. (S4 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Contact/severity + burial; no interface bonus</t>
+          <t>Screen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14/3</t>
+          <t>TP/FN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>FP/TN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>Sensitivity</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.600</t>
+          <t>Specificity</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>PPV</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>Balanced accuracy</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>Within-system p</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Any pLDDT-passing interface</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15/2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7/23</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.882</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.767</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.682</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Contact/severity + burial; no interface bonus</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>14/3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.600</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.538</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.712</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.129</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Full Tier 1-2 screen</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>17/0</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>13/17</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>1.000</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.567</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0.567</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0.783</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0.0095</t>
         </is>
@@ -6467,10 +6529,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="51" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
@@ -6478,108 +6540,115 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Analysis convention</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Whole-variant score</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Monomer fold</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>All energetic outputs</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Four-output continuity aggregate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Primary 57-variant graded cohort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>41.0/57 = 0.719</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>19/25 = 0.760</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>58/77 = 0.753</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>92/124 = 0.742</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S1 Table, denominator_sensitivity sheet. Denominator and eligibility sensitivity analyses. (S5 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All-row output convention</t>
+          <t>Analysis convention</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Whole-variant exclusions retained</t>
+          <t>Whole-variant score</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19/26 = 0.731</t>
+          <t>Monomer fold</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58/78 = 0.744</t>
+          <t>All energetic outputs</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>92/125 = 0.736</t>
+          <t>Four-output continuity aggregate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Primary 57-variant graded cohort</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>41.0/57 = 0.719</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>19/25 = 0.760</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>58/77 = 0.753</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>92/124 = 0.742</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>All-row output convention</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Whole-variant exclusions retained</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19/26 = 0.731</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>58/78 = 0.744</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>92/125 = 0.736</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Include BRCA1 R1699L/Q in rubric-only sensitivity</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>43.0/59 = 0.729</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Measured axes remain available</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Not used as headline</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Not used as headline</t>
         </is>
@@ -6596,101 +6665,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Variant</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Axis</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Measured or curated expectation</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Predicted ΔΔG (kcal/mol)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BRCA1 V1736A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Monomer fold</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Genuine magnitude miss; false negative at 2.5.</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>S1 Table, fold_binding_disagreements sheet. Directly measured or curated fold and binding disagreements at the 2.5 kcal/mol reference. (S6 Table in the reviewed manuscript.)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLH1 R755W</t>
+          <t>Variant</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Monomer fold</t>
+          <t>Axis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Curated destabilizing</t>
+          <t>Measured or curated expectation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>Predicted ΔΔG (kcal/mol)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Genuine miss against the curated fold mechanism.</t>
+          <t>Interpretation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BRCA1 R1751Q</t>
+          <t>BRCA1 V1736A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6700,24 +6722,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Both values below 2.5; imperfect grade arises from sign-based ground truth.</t>
+          <t>Genuine magnitude miss; false negative at 2.5.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BRCA1 L1664P</t>
+          <t>MLH1 R755W</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6727,96 +6749,150 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>Curated destabilizing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Both values below 2.5; imperfect grade arises from sign-based ground truth.</t>
+          <t>Genuine miss against the curated fold mechanism.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HBB N102T</t>
+          <t>BRCA1 R1751Q</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Binding</t>
+          <t>Monomer fold</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sub-threshold destabilization under the sign-based convention.</t>
+          <t>Both values below 2.5; imperfect grade arises from sign-based ground truth.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HBB W37Y</t>
+          <t>BRCA1 L1664P</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Binding</t>
+          <t>Monomer fold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sub-threshold destabilization under the sign-based convention.</t>
+          <t>Both values below 2.5; imperfect grade arises from sign-based ground truth.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>HBB N102T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Binding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sub-threshold destabilization under the sign-based convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HBB W37Y</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Binding</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sub-threshold destabilization under the sign-based convention.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>MSH2 A636P</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Monomer and complex-context fold</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Neutral on both modeled fold axes</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>4.89 / 5.38</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Literature-supported neutral expectations; false-positive fold signals. The mismatch-processing defect lies outside the modeled axes.</t>
         </is>

--- a/submission/COMAVI_v7.12_SI/S1_Table.xlsx
+++ b/submission/COMAVI_v7.12_SI/S1_Table.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -615,12 +615,13 @@
     <col width="46" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>S1 Table, benchmark_variants sheet. The 61 benchmark variants. Every variant scored in this paper, with the clinical annotation, the expected mechanism defined from primary literature before COMAVI results were considered, the structural-context tier, COMAVI's graded agreement at the 2.5 kcal/mol reference threshold, and the (S1 Table in the reviewed manuscript.)</t>
+          <t>S1 Table, benchmark_variants sheet. The 61 benchmark variants. Every variant scored in this paper, with the clinical annotation, the expected mechanism defined from primary literature before COMAVI results were considered, the structural-context tier, COMAVI's graded agreement at the 2.5 kcal/mol reference threshold, and the (S1 Table in the reviewed manuscript.) AlphaMissense pathogenicity scores are given per variant where AlphaMissense covers the substitution.</t>
         </is>
       </c>
     </row>
@@ -710,6 +711,11 @@
           <t>Structure</t>
         </is>
       </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>AlphaMissense</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -797,6 +803,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -884,6 +895,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -971,6 +987,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1058,6 +1079,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1145,6 +1171,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1232,6 +1263,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1319,6 +1355,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1406,6 +1447,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1493,6 +1539,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1580,6 +1631,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1667,6 +1723,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1754,6 +1815,11 @@
           <t>1JNX.pdb</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1841,6 +1907,9 @@
           <t>1JM7.pdb</t>
         </is>
       </c>
+      <c r="R16" t="n">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1928,6 +1997,9 @@
           <t>1JM7.pdb</t>
         </is>
       </c>
+      <c r="R17" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2015,6 +2087,9 @@
           <t>1JM7.pdb</t>
         </is>
       </c>
+      <c r="R18" t="n">
+        <v>0.081</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2102,6 +2177,9 @@
           <t>1JM7.pdb</t>
         </is>
       </c>
+      <c r="R19" t="n">
+        <v>0.705</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2189,6 +2267,9 @@
           <t>fold_calm1_cacna1c_model_0.pdb</t>
         </is>
       </c>
+      <c r="R20" t="n">
+        <v>0.984</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2276,6 +2357,9 @@
           <t>fold_calm1_cacna1c_model_0.pdb</t>
         </is>
       </c>
+      <c r="R21" t="n">
+        <v>0.998</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2363,6 +2447,9 @@
           <t>fold_calm1_cacna1c_model_0.pdb</t>
         </is>
       </c>
+      <c r="R22" t="n">
+        <v>0.209</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2450,6 +2537,9 @@
           <t>2WII_trim.pdb</t>
         </is>
       </c>
+      <c r="R23" t="n">
+        <v>0.059</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2537,6 +2627,9 @@
           <t>2WII_trim.pdb</t>
         </is>
       </c>
+      <c r="R24" t="n">
+        <v>0.243</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2624,6 +2717,9 @@
           <t>2WII_trim.pdb</t>
         </is>
       </c>
+      <c r="R25" t="n">
+        <v>0.398</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2711,6 +2807,9 @@
           <t>2HHB.pdb</t>
         </is>
       </c>
+      <c r="R26" t="n">
+        <v>0.223</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2798,6 +2897,9 @@
           <t>2HHB.pdb</t>
         </is>
       </c>
+      <c r="R27" t="n">
+        <v>0.969</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2885,6 +2987,9 @@
           <t>2HHB.pdb</t>
         </is>
       </c>
+      <c r="R28" t="n">
+        <v>0.969</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2972,6 +3077,9 @@
           <t>2HHB.pdb</t>
         </is>
       </c>
+      <c r="R29" t="n">
+        <v>0.993</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3059,6 +3167,9 @@
           <t>2HHB.pdb</t>
         </is>
       </c>
+      <c r="R30" t="n">
+        <v>0.9399999999999999</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3146,6 +3257,9 @@
           <t>2HHB.pdb</t>
         </is>
       </c>
+      <c r="R31" t="n">
+        <v>0.894</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3233,6 +3347,9 @@
           <t>6XI7.pdb</t>
         </is>
       </c>
+      <c r="R32" t="n">
+        <v>0.998</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3320,6 +3437,9 @@
           <t>6XI7.pdb</t>
         </is>
       </c>
+      <c r="R33" t="n">
+        <v>0.995</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3407,6 +3527,9 @@
           <t>6XI7.pdb</t>
         </is>
       </c>
+      <c r="R34" t="n">
+        <v>0.998</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3494,6 +3617,9 @@
           <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
+      <c r="R35" t="n">
+        <v>0.077</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3581,6 +3707,9 @@
           <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
+      <c r="R36" t="n">
+        <v>0.225</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3668,6 +3797,9 @@
           <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
+      <c r="R37" t="n">
+        <v>0.649</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3755,6 +3887,9 @@
           <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
+      <c r="R38" t="n">
+        <v>0.999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3842,6 +3977,9 @@
           <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
+      <c r="R39" t="n">
+        <v>0.918</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3929,6 +4067,9 @@
           <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
+      <c r="R40" t="n">
+        <v>0.986</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4016,6 +4157,9 @@
           <t>fold_mlh1_pms2_model_0.pdb</t>
         </is>
       </c>
+      <c r="R41" t="n">
+        <v>0.988</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4103,6 +4247,9 @@
           <t>fold_msh2_msh6_model_0.pdb</t>
         </is>
       </c>
+      <c r="R42" t="n">
+        <v>0.896</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4190,6 +4337,9 @@
           <t>fold_msh2_msh6_model_0.pdb</t>
         </is>
       </c>
+      <c r="R43" t="n">
+        <v>0.991</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4277,6 +4427,9 @@
           <t>fold_msh2_msh6_model_0.pdb</t>
         </is>
       </c>
+      <c r="R44" t="n">
+        <v>0.323</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4364,6 +4517,9 @@
           <t>fold_msh2_msh6_model_0.pdb</t>
         </is>
       </c>
+      <c r="R45" t="n">
+        <v>0.999</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4451,6 +4607,9 @@
           <t>fold_msh2_msh6_model_0.pdb</t>
         </is>
       </c>
+      <c r="R46" t="n">
+        <v>0.348</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4538,6 +4697,9 @@
           <t>fold_pik3ca_pik3r1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R47" t="n">
+        <v>0.9409999999999999</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4625,6 +4787,9 @@
           <t>fold_pik3ca_pik3r1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R48" t="n">
+        <v>0.988</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4712,6 +4877,9 @@
           <t>fold_pik3ca_pik3r1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R49" t="n">
+        <v>0.538</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4799,6 +4967,9 @@
           <t>fold_pik3ca_pik3r1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R50" t="n">
+        <v>0.253</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4886,6 +5057,9 @@
           <t>fold_pik3ca_pik3r1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R51" t="n">
+        <v>0.999</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4973,6 +5147,9 @@
           <t>fold_smad4_smad3_model_0.pdb</t>
         </is>
       </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5060,6 +5237,9 @@
           <t>fold_smad4_smad3_model_0.pdb</t>
         </is>
       </c>
+      <c r="R53" t="n">
+        <v>0.991</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5147,6 +5327,9 @@
           <t>fold_smad4_smad3_model_0.pdb</t>
         </is>
       </c>
+      <c r="R54" t="n">
+        <v>0.616</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5234,6 +5417,9 @@
           <t>fold_smad4_smad3_model_0.pdb</t>
         </is>
       </c>
+      <c r="R55" t="n">
+        <v>0.998</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5321,6 +5507,9 @@
           <t>fold_tnni3_tnnc1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R56" t="n">
+        <v>0.127</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5408,6 +5597,9 @@
           <t>fold_tnni3_tnnc1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R57" t="n">
+        <v>0.971</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5495,6 +5687,9 @@
           <t>fold_tnni3_tnnc1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R58" t="n">
+        <v>0.6870000000000001</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5582,6 +5777,9 @@
           <t>fold_tnni3_tnnc1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R59" t="n">
+        <v>0.411</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5669,6 +5867,9 @@
           <t>fold_vhl_tceb1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R60" t="n">
+        <v>0.996</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5756,6 +5957,9 @@
           <t>fold_vhl_tceb1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R61" t="n">
+        <v>0.999</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5843,6 +6047,9 @@
           <t>fold_vhl_tceb1_model_0.pdb</t>
         </is>
       </c>
+      <c r="R62" t="n">
+        <v>0.973</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5930,6 +6137,11 @@
           <t>1SQ0.pdb</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6015,6 +6227,11 @@
       <c r="Q64" t="inlineStr">
         <is>
           <t>1SQ0.pdb</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
